--- a/outputs/analysis/analysis_output/tables/part2/cao_salary_table_presence.xlsx
+++ b/outputs/analysis/analysis_output/tables/part2/cao_salary_table_presence.xlsx
@@ -566,13 +566,13 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C2" t="n">
         <v>32</v>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -594,13 +594,13 @@
         <v>21</v>
       </c>
       <c r="B4" t="n">
-        <v>100</v>
+        <v>92.85714285714286</v>
       </c>
       <c r="C4" t="n">
         <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
@@ -636,13 +636,13 @@
         <v>41</v>
       </c>
       <c r="B7" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C7" t="n">
         <v>20</v>
       </c>
       <c r="D7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -664,13 +664,13 @@
         <v>50</v>
       </c>
       <c r="B9" t="n">
-        <v>100</v>
+        <v>91.66666666666666</v>
       </c>
       <c r="C9" t="n">
         <v>12</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -678,13 +678,13 @@
         <v>51</v>
       </c>
       <c r="B10" t="n">
-        <v>57.14285714285714</v>
+        <v>90.47619047619048</v>
       </c>
       <c r="C10" t="n">
         <v>21</v>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
@@ -692,13 +692,13 @@
         <v>80</v>
       </c>
       <c r="B11" t="n">
-        <v>100</v>
+        <v>92.30769230769231</v>
       </c>
       <c r="C11" t="n">
         <v>13</v>
       </c>
       <c r="D11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -706,13 +706,13 @@
         <v>83</v>
       </c>
       <c r="B12" t="n">
-        <v>100</v>
+        <v>92.85714285714286</v>
       </c>
       <c r="C12" t="n">
         <v>14</v>
       </c>
       <c r="D12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
@@ -734,13 +734,13 @@
         <v>156</v>
       </c>
       <c r="B14" t="n">
-        <v>44.44444444444444</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="C14" t="n">
         <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
@@ -748,13 +748,13 @@
         <v>157</v>
       </c>
       <c r="B15" t="n">
-        <v>82.35294117647058</v>
+        <v>100</v>
       </c>
       <c r="C15" t="n">
         <v>17</v>
       </c>
       <c r="D15" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
@@ -762,13 +762,13 @@
         <v>163</v>
       </c>
       <c r="B16" t="n">
-        <v>9.090909090909092</v>
+        <v>100</v>
       </c>
       <c r="C16" t="n">
         <v>11</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17">
@@ -790,13 +790,13 @@
         <v>214</v>
       </c>
       <c r="B18" t="n">
-        <v>71.42857142857143</v>
+        <v>90.47619047619048</v>
       </c>
       <c r="C18" t="n">
         <v>21</v>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19">
@@ -804,13 +804,13 @@
         <v>218</v>
       </c>
       <c r="B19" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C19" t="n">
         <v>12</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20">
@@ -832,13 +832,13 @@
         <v>234</v>
       </c>
       <c r="B21" t="n">
-        <v>10</v>
+        <v>95</v>
       </c>
       <c r="C21" t="n">
         <v>20</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22">
@@ -846,13 +846,13 @@
         <v>243</v>
       </c>
       <c r="B22" t="n">
-        <v>100</v>
+        <v>96.15384615384616</v>
       </c>
       <c r="C22" t="n">
         <v>26</v>
       </c>
       <c r="D22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23">
@@ -874,13 +874,13 @@
         <v>254</v>
       </c>
       <c r="B24" t="n">
-        <v>80.95238095238095</v>
+        <v>100</v>
       </c>
       <c r="C24" t="n">
         <v>21</v>
       </c>
       <c r="D24" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25">
@@ -888,13 +888,13 @@
         <v>301</v>
       </c>
       <c r="B25" t="n">
-        <v>53.84615384615385</v>
+        <v>96.15384615384616</v>
       </c>
       <c r="C25" t="n">
         <v>26</v>
       </c>
       <c r="D25" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26">
@@ -902,13 +902,13 @@
         <v>306</v>
       </c>
       <c r="B26" t="n">
-        <v>57.14285714285714</v>
+        <v>100</v>
       </c>
       <c r="C26" t="n">
         <v>14</v>
       </c>
       <c r="D26" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27">
@@ -930,13 +930,13 @@
         <v>317</v>
       </c>
       <c r="B28" t="n">
-        <v>92.85714285714286</v>
+        <v>69.23076923076923</v>
       </c>
       <c r="C28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D28" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29">
@@ -944,13 +944,13 @@
         <v>331</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C29" t="n">
         <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -986,13 +986,13 @@
         <v>433</v>
       </c>
       <c r="B32" t="n">
-        <v>78.57142857142857</v>
+        <v>96.42857142857143</v>
       </c>
       <c r="C32" t="n">
         <v>28</v>
       </c>
       <c r="D32" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33">
@@ -1042,13 +1042,13 @@
         <v>496</v>
       </c>
       <c r="B36" t="n">
-        <v>28</v>
+        <v>96</v>
       </c>
       <c r="C36" t="n">
         <v>25</v>
       </c>
       <c r="D36" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37">
@@ -1084,13 +1084,13 @@
         <v>526</v>
       </c>
       <c r="B39" t="n">
-        <v>44.44444444444444</v>
+        <v>94.44444444444444</v>
       </c>
       <c r="C39" t="n">
         <v>18</v>
       </c>
       <c r="D39" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="40">
@@ -1210,13 +1210,13 @@
         <v>625</v>
       </c>
       <c r="B48" t="n">
-        <v>9.090909090909092</v>
+        <v>100</v>
       </c>
       <c r="C48" t="n">
         <v>11</v>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="49">
@@ -1252,13 +1252,13 @@
         <v>637</v>
       </c>
       <c r="B51" t="n">
-        <v>88.23529411764706</v>
+        <v>100</v>
       </c>
       <c r="C51" t="n">
         <v>17</v>
       </c>
       <c r="D51" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="52">
@@ -1280,13 +1280,13 @@
         <v>679</v>
       </c>
       <c r="B53" t="n">
-        <v>96.42857142857143</v>
+        <v>100</v>
       </c>
       <c r="C53" t="n">
         <v>28</v>
       </c>
       <c r="D53" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="54">
@@ -1308,13 +1308,13 @@
         <v>721</v>
       </c>
       <c r="B55" t="n">
-        <v>22.22222222222222</v>
+        <v>94.44444444444444</v>
       </c>
       <c r="C55" t="n">
         <v>18</v>
       </c>
       <c r="D55" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="56">
@@ -1322,13 +1322,13 @@
         <v>725</v>
       </c>
       <c r="B56" t="n">
-        <v>100</v>
+        <v>95.65217391304348</v>
       </c>
       <c r="C56" t="n">
         <v>23</v>
       </c>
       <c r="D56" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="57">
@@ -1336,13 +1336,13 @@
         <v>727</v>
       </c>
       <c r="B57" t="n">
-        <v>100</v>
+        <v>97.22222222222221</v>
       </c>
       <c r="C57" t="n">
         <v>36</v>
       </c>
       <c r="D57" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="58">
@@ -1350,13 +1350,13 @@
         <v>730</v>
       </c>
       <c r="B58" t="n">
-        <v>76.47058823529412</v>
+        <v>88.23529411764706</v>
       </c>
       <c r="C58" t="n">
         <v>17</v>
       </c>
       <c r="D58" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="59">
@@ -1364,13 +1364,13 @@
         <v>748</v>
       </c>
       <c r="B59" t="n">
-        <v>17.64705882352941</v>
+        <v>94.11764705882352</v>
       </c>
       <c r="C59" t="n">
         <v>17</v>
       </c>
       <c r="D59" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="60">
@@ -1378,13 +1378,13 @@
         <v>750</v>
       </c>
       <c r="B60" t="n">
-        <v>7.692307692307693</v>
+        <v>95.83333333333334</v>
       </c>
       <c r="C60" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D60" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="61">
@@ -1392,13 +1392,13 @@
         <v>759</v>
       </c>
       <c r="B61" t="n">
-        <v>100</v>
+        <v>95.83333333333334</v>
       </c>
       <c r="C61" t="n">
         <v>24</v>
       </c>
       <c r="D61" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="62">
@@ -1420,10 +1420,10 @@
         <v>822</v>
       </c>
       <c r="B63" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="C63" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D63" t="n">
         <v>14</v>
@@ -1462,13 +1462,13 @@
         <v>826</v>
       </c>
       <c r="B66" t="n">
-        <v>94.11764705882352</v>
+        <v>100</v>
       </c>
       <c r="C66" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D66" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="67">
@@ -1532,13 +1532,13 @@
         <v>1022</v>
       </c>
       <c r="B71" t="n">
-        <v>46.66666666666666</v>
+        <v>90.90909090909091</v>
       </c>
       <c r="C71" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D71" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="72">
@@ -1546,13 +1546,13 @@
         <v>1060</v>
       </c>
       <c r="B72" t="n">
-        <v>40</v>
+        <v>38.09523809523809</v>
       </c>
       <c r="C72" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D72" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="73">
@@ -1560,13 +1560,13 @@
         <v>1165</v>
       </c>
       <c r="B73" t="n">
-        <v>78.57142857142857</v>
+        <v>92</v>
       </c>
       <c r="C73" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D73" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="74">
@@ -1574,13 +1574,13 @@
         <v>1188</v>
       </c>
       <c r="B74" t="n">
-        <v>55.55555555555556</v>
+        <v>87.5</v>
       </c>
       <c r="C74" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D74" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75">
@@ -1591,10 +1591,10 @@
         <v>100</v>
       </c>
       <c r="C75" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D75" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="76">
@@ -1602,13 +1602,13 @@
         <v>1287</v>
       </c>
       <c r="B76" t="n">
-        <v>94.44444444444444</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="C76" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D76" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="77">
@@ -1619,7 +1619,7 @@
         <v>0</v>
       </c>
       <c r="C77" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D77" t="n">
         <v>0</v>
@@ -1630,13 +1630,13 @@
         <v>1296</v>
       </c>
       <c r="B78" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="C78" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79">
@@ -1644,13 +1644,13 @@
         <v>1345</v>
       </c>
       <c r="B79" t="n">
-        <v>42.85714285714285</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="C79" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D79" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80">
@@ -1661,10 +1661,10 @@
         <v>100</v>
       </c>
       <c r="C80" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D80" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="81">
@@ -1672,10 +1672,10 @@
         <v>1471</v>
       </c>
       <c r="B81" t="n">
-        <v>83.33333333333334</v>
+        <v>100</v>
       </c>
       <c r="C81" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D81" t="n">
         <v>10</v>
@@ -1686,13 +1686,13 @@
         <v>1494</v>
       </c>
       <c r="B82" t="n">
-        <v>27.77777777777778</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="C82" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D82" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="83">
@@ -1700,13 +1700,13 @@
         <v>1496</v>
       </c>
       <c r="B83" t="n">
-        <v>77.77777777777779</v>
+        <v>90</v>
       </c>
       <c r="C83" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D83" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="84">
@@ -1717,10 +1717,10 @@
         <v>100</v>
       </c>
       <c r="C84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -1728,13 +1728,13 @@
         <v>1536</v>
       </c>
       <c r="B85" t="n">
-        <v>23.07692307692308</v>
+        <v>100</v>
       </c>
       <c r="C85" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D85" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="86">
@@ -1742,13 +1742,13 @@
         <v>1547</v>
       </c>
       <c r="B86" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="C86" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D86" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="87">
@@ -1756,13 +1756,13 @@
         <v>1574</v>
       </c>
       <c r="B87" t="n">
-        <v>81.81818181818183</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="C87" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D87" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="88">
@@ -1770,13 +1770,13 @@
         <v>1612</v>
       </c>
       <c r="B88" t="n">
-        <v>61.90476190476191</v>
+        <v>100</v>
       </c>
       <c r="C88" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D88" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="89">
@@ -1784,13 +1784,13 @@
         <v>1618</v>
       </c>
       <c r="B89" t="n">
-        <v>10</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="C89" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D89" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90">
@@ -1801,10 +1801,10 @@
         <v>100</v>
       </c>
       <c r="C90" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D90" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="91">
@@ -1812,13 +1812,13 @@
         <v>1869</v>
       </c>
       <c r="B91" t="n">
-        <v>100</v>
+        <v>93.75</v>
       </c>
       <c r="C91" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D91" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="92">
@@ -1826,13 +1826,13 @@
         <v>1944</v>
       </c>
       <c r="B92" t="n">
-        <v>65.51724137931035</v>
+        <v>91.66666666666666</v>
       </c>
       <c r="C92" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D92" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="93">
@@ -1843,10 +1843,10 @@
         <v>100</v>
       </c>
       <c r="C93" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D93" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="94">
@@ -1854,10 +1854,10 @@
         <v>2070</v>
       </c>
       <c r="B94" t="n">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="C94" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D94" t="n">
         <v>7</v>
@@ -1868,13 +1868,13 @@
         <v>2266</v>
       </c>
       <c r="B95" t="n">
-        <v>92.30769230769231</v>
+        <v>90</v>
       </c>
       <c r="C95" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D95" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="96">
@@ -1885,10 +1885,10 @@
         <v>100</v>
       </c>
       <c r="C96" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D96" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="97">
@@ -1896,13 +1896,13 @@
         <v>2535</v>
       </c>
       <c r="B97" t="n">
-        <v>19.04761904761905</v>
+        <v>94.11764705882352</v>
       </c>
       <c r="C97" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D97" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="98">
@@ -1910,13 +1910,13 @@
         <v>2948</v>
       </c>
       <c r="B98" t="n">
-        <v>97.29729729729731</v>
+        <v>89.65517241379311</v>
       </c>
       <c r="C98" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D98" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="99">
@@ -1924,13 +1924,13 @@
         <v>3313</v>
       </c>
       <c r="B99" t="n">
-        <v>21.42857142857143</v>
+        <v>7.692307692307693</v>
       </c>
       <c r="C99" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D99" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -1938,13 +1938,13 @@
         <v>3335</v>
       </c>
       <c r="B100" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="C100" t="n">
         <v>10</v>
       </c>
       <c r="D100" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
